--- a/data/weekly_report.xlsx
+++ b/data/weekly_report.xlsx
@@ -500,44 +500,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100000</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>15.79</v>
+        <v>11.11</v>
       </c>
       <c r="H2" t="n">
-        <v>-237.19</v>
+        <v>-168.15</v>
       </c>
       <c r="I2" t="n">
-        <v>247.91</v>
+        <v>85.84</v>
       </c>
       <c r="J2" t="n">
-        <v>100774.35</v>
+        <v>100389.56</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>CRCL $57.14</t>
+          <t>VICI $47.79</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ZM $-28.95</t>
+          <t>KGC $-40.71</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,25 +672,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>YETI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>77.56</v>
+        <v>44.79</v>
       </c>
       <c r="D3" t="n">
-        <v>73.682</v>
+        <v>50.12</v>
       </c>
       <c r="E3" t="n">
-        <v>85.316</v>
+        <v>34.13</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46247</v>
@@ -714,28 +714,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>YETI</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>44.79</v>
+        <v>200.37</v>
       </c>
       <c r="D4" t="n">
-        <v>50.12</v>
+        <v>190.3515</v>
       </c>
       <c r="E4" t="n">
-        <v>34.13</v>
+        <v>220.407</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -765,19 +765,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200.37</v>
+        <v>27.2</v>
       </c>
       <c r="D5" t="n">
-        <v>190.3515</v>
+        <v>25.84</v>
       </c>
       <c r="E5" t="n">
-        <v>220.407</v>
+        <v>29.92</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>68.65000000000001</v>
+        <v>269.77</v>
       </c>
       <c r="D6" t="n">
-        <v>65.2175</v>
+        <v>256.2815</v>
       </c>
       <c r="E6" t="n">
-        <v>75.515</v>
+        <v>296.747</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>CDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,19 +849,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.2</v>
+        <v>20.33</v>
       </c>
       <c r="D7" t="n">
-        <v>25.84</v>
+        <v>18.5138</v>
       </c>
       <c r="E7" t="n">
-        <v>29.92</v>
+        <v>23.3695</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>FSM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11.77</v>
+        <v>11.49</v>
       </c>
       <c r="D8" t="n">
-        <v>11.1815</v>
+        <v>10.4502</v>
       </c>
       <c r="E8" t="n">
-        <v>12.947</v>
+        <v>13.2035</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -933,19 +933,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>34.96</v>
+        <v>235.46</v>
       </c>
       <c r="D9" t="n">
-        <v>33.212</v>
+        <v>223.687</v>
       </c>
       <c r="E9" t="n">
-        <v>38.456</v>
+        <v>259.006</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -975,19 +975,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>78.70999999999999</v>
+        <v>29.07</v>
       </c>
       <c r="D10" t="n">
-        <v>83.1178</v>
+        <v>30.5235</v>
       </c>
       <c r="E10" t="n">
-        <v>69.89449999999999</v>
+        <v>26.163</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1008,28 +1008,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>269.77</v>
+        <v>145.21</v>
       </c>
       <c r="D11" t="n">
-        <v>256.2815</v>
+        <v>152.4705</v>
       </c>
       <c r="E11" t="n">
-        <v>296.747</v>
+        <v>130.689</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1059,19 +1059,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20.33</v>
+        <v>140.45</v>
       </c>
       <c r="D12" t="n">
-        <v>18.5138</v>
+        <v>108.9013</v>
       </c>
       <c r="E12" t="n">
-        <v>23.3695</v>
+        <v>161.5075</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1092,28 +1092,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>45.06</v>
+        <v>10.17</v>
       </c>
       <c r="D13" t="n">
-        <v>42.0885</v>
+        <v>10.6785</v>
       </c>
       <c r="E13" t="n">
-        <v>51.0029</v>
+        <v>9.153</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1130,972 +1130,6 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AG</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>18.4794</v>
-      </c>
-      <c r="E14" t="n">
-        <v>23.105</v>
-      </c>
-      <c r="F14" t="n">
-        <v>24</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>46253</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>KGC</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>29.67</v>
-      </c>
-      <c r="D15" t="n">
-        <v>27.1256</v>
-      </c>
-      <c r="E15" t="n">
-        <v>34.1105</v>
-      </c>
-      <c r="F15" t="n">
-        <v>16</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>46253</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>KVUE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="D16" t="n">
-        <v>18.0975</v>
-      </c>
-      <c r="E16" t="n">
-        <v>20.955</v>
-      </c>
-      <c r="F16" t="n">
-        <v>26</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>46253</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>FSM</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4502</v>
-      </c>
-      <c r="E17" t="n">
-        <v>13.2035</v>
-      </c>
-      <c r="F17" t="n">
-        <v>43</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>46253</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>39.93</v>
-      </c>
-      <c r="D18" t="n">
-        <v>41.9265</v>
-      </c>
-      <c r="E18" t="n">
-        <v>35.937</v>
-      </c>
-      <c r="F18" t="n">
-        <v>12</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="D19" t="n">
-        <v>22.6575</v>
-      </c>
-      <c r="E19" t="n">
-        <v>26.235</v>
-      </c>
-      <c r="F19" t="n">
-        <v>20</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>OXY</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>61.69</v>
-      </c>
-      <c r="D20" t="n">
-        <v>58.6055</v>
-      </c>
-      <c r="E20" t="n">
-        <v>67.85899999999999</v>
-      </c>
-      <c r="F20" t="n">
-        <v>8</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>134.8</v>
-      </c>
-      <c r="D21" t="n">
-        <v>128.06</v>
-      </c>
-      <c r="E21" t="n">
-        <v>148.28</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>37.16</v>
-      </c>
-      <c r="D22" t="n">
-        <v>35.302</v>
-      </c>
-      <c r="E22" t="n">
-        <v>40.876</v>
-      </c>
-      <c r="F22" t="n">
-        <v>13</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>VALE</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="D23" t="n">
-        <v>13.889</v>
-      </c>
-      <c r="E23" t="n">
-        <v>16.082</v>
-      </c>
-      <c r="F23" t="n">
-        <v>34</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ROST</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>235.46</v>
-      </c>
-      <c r="D24" t="n">
-        <v>223.687</v>
-      </c>
-      <c r="E24" t="n">
-        <v>259.006</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>81.26000000000001</v>
-      </c>
-      <c r="D25" t="n">
-        <v>77.197</v>
-      </c>
-      <c r="E25" t="n">
-        <v>89.386</v>
-      </c>
-      <c r="F25" t="n">
-        <v>6</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TECK</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>68.59</v>
-      </c>
-      <c r="D26" t="n">
-        <v>65.1605</v>
-      </c>
-      <c r="E26" t="n">
-        <v>75.449</v>
-      </c>
-      <c r="F26" t="n">
-        <v>7</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>186.64</v>
-      </c>
-      <c r="D27" t="n">
-        <v>177.308</v>
-      </c>
-      <c r="E27" t="n">
-        <v>205.304</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>110.29</v>
-      </c>
-      <c r="D28" t="n">
-        <v>104.7755</v>
-      </c>
-      <c r="E28" t="n">
-        <v>121.319</v>
-      </c>
-      <c r="F28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>29.07</v>
-      </c>
-      <c r="D29" t="n">
-        <v>30.5235</v>
-      </c>
-      <c r="E29" t="n">
-        <v>26.163</v>
-      </c>
-      <c r="F29" t="n">
-        <v>17</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ONON</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>28.79</v>
-      </c>
-      <c r="D30" t="n">
-        <v>30.2295</v>
-      </c>
-      <c r="E30" t="n">
-        <v>25.911</v>
-      </c>
-      <c r="F30" t="n">
-        <v>17</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>145.21</v>
-      </c>
-      <c r="D31" t="n">
-        <v>152.4705</v>
-      </c>
-      <c r="E31" t="n">
-        <v>130.689</v>
-      </c>
-      <c r="F31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>VICI</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>26.55</v>
-      </c>
-      <c r="D32" t="n">
-        <v>27.8775</v>
-      </c>
-      <c r="E32" t="n">
-        <v>23.895</v>
-      </c>
-      <c r="F32" t="n">
-        <v>18</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>50.37</v>
-      </c>
-      <c r="D33" t="n">
-        <v>47.8515</v>
-      </c>
-      <c r="E33" t="n">
-        <v>55.407</v>
-      </c>
-      <c r="F33" t="n">
-        <v>9</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AMRZ</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>43.85</v>
-      </c>
-      <c r="D34" t="n">
-        <v>46.0425</v>
-      </c>
-      <c r="E34" t="n">
-        <v>39.465</v>
-      </c>
-      <c r="F34" t="n">
-        <v>11</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ANF</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>140.45</v>
-      </c>
-      <c r="D35" t="n">
-        <v>108.9013</v>
-      </c>
-      <c r="E35" t="n">
-        <v>161.5075</v>
-      </c>
-      <c r="F35" t="n">
-        <v>3</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ERIC</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="D36" t="n">
-        <v>10.6785</v>
-      </c>
-      <c r="E36" t="n">
-        <v>9.153</v>
-      </c>
-      <c r="F36" t="n">
-        <v>49</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2108,7 +1142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2186,7 +1220,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2195,19 +1229,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>59.92</v>
+        <v>34.96</v>
       </c>
       <c r="D2" t="n">
-        <v>56.924</v>
+        <v>33.212</v>
       </c>
       <c r="E2" t="n">
-        <v>65.91200000000001</v>
+        <v>38.456</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2220,10 +1254,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46265</v>
+        <v>46287</v>
       </c>
       <c r="K2" t="n">
-        <v>56.924</v>
+        <v>33.212</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -2231,7 +1265,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-23.97</v>
+        <v>-24.47</v>
       </c>
       <c r="N2" t="n">
         <v>-5</v>
@@ -2240,7 +1274,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2249,19 +1283,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32.31</v>
+        <v>45.06</v>
       </c>
       <c r="D3" t="n">
-        <v>30.6945</v>
+        <v>42.0885</v>
       </c>
       <c r="E3" t="n">
-        <v>35.541</v>
+        <v>51.0029</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2274,10 +1308,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46265</v>
+        <v>46289</v>
       </c>
       <c r="K3" t="n">
-        <v>30.6945</v>
+        <v>42.0885</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -2285,16 +1319,16 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>-24.23</v>
+        <v>-32.69</v>
       </c>
       <c r="N3" t="n">
-        <v>-5</v>
+        <v>-6.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PBR-A</t>
+          <t>KGC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2303,23 +1337,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.52</v>
+        <v>29.67</v>
       </c>
       <c r="D4" t="n">
-        <v>15.694</v>
+        <v>27.1256</v>
       </c>
       <c r="E4" t="n">
-        <v>18.172</v>
+        <v>34.1105</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Closed (Take-Profit)</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2328,27 +1362,27 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46266</v>
+        <v>46289</v>
       </c>
       <c r="K4" t="n">
-        <v>18.172</v>
+        <v>27.1256</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Take-Profit</t>
+          <t>Stop-Loss</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>49.56</v>
+        <v>-40.71</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SKHY</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2357,23 +1391,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>156.94</v>
+        <v>23.85</v>
       </c>
       <c r="D5" t="n">
-        <v>149.093</v>
+        <v>22.6575</v>
       </c>
       <c r="E5" t="n">
-        <v>172.634</v>
+        <v>26.235</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Closed (Take-Profit)</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2382,27 +1416,27 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46269</v>
+        <v>46286</v>
       </c>
       <c r="K5" t="n">
-        <v>172.634</v>
+        <v>22.6575</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Take-Profit</t>
+          <t>Stop-Loss</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>47.08</v>
+        <v>-23.85</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2411,16 +1445,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.68</v>
+        <v>61.69</v>
       </c>
       <c r="D6" t="n">
-        <v>19.646</v>
+        <v>58.6055</v>
       </c>
       <c r="E6" t="n">
-        <v>22.748</v>
+        <v>67.85899999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46254</v>
@@ -2436,10 +1470,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46266</v>
+        <v>46286</v>
       </c>
       <c r="K6" t="n">
-        <v>19.646</v>
+        <v>58.6055</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -2447,7 +1481,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-24.82</v>
+        <v>-24.68</v>
       </c>
       <c r="N6" t="n">
         <v>-5</v>
@@ -2456,7 +1490,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2465,16 +1499,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53.58</v>
+        <v>134.8</v>
       </c>
       <c r="D7" t="n">
-        <v>50.901</v>
+        <v>128.06</v>
       </c>
       <c r="E7" t="n">
-        <v>58.938</v>
+        <v>148.28</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46254</v>
@@ -2490,10 +1524,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46266</v>
+        <v>46287</v>
       </c>
       <c r="K7" t="n">
-        <v>50.901</v>
+        <v>128.06</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -2501,7 +1535,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-24.11</v>
+        <v>-20.22</v>
       </c>
       <c r="N7" t="n">
         <v>-5</v>
@@ -2510,7 +1544,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>VALE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2519,23 +1553,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>89.38</v>
+        <v>14.62</v>
       </c>
       <c r="D8" t="n">
-        <v>83.6656</v>
+        <v>13.889</v>
       </c>
       <c r="E8" t="n">
-        <v>100.8087</v>
+        <v>16.082</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Closed (Take-Profit)</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2544,27 +1578,27 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46268</v>
+        <v>46288</v>
       </c>
       <c r="K8" t="n">
-        <v>100.8087</v>
+        <v>13.889</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Take-Profit</t>
+          <t>Stop-Loss</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>57.14</v>
+        <v>-24.85</v>
       </c>
       <c r="N8" t="n">
-        <v>12.79</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TTD</t>
+          <t>ONON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2573,19 +1607,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13.24</v>
+        <v>28.79</v>
       </c>
       <c r="D9" t="n">
-        <v>13.902</v>
+        <v>30.2295</v>
       </c>
       <c r="E9" t="n">
-        <v>11.916</v>
+        <v>25.911</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2598,10 +1632,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46267</v>
+        <v>46290</v>
       </c>
       <c r="K9" t="n">
-        <v>13.902</v>
+        <v>30.2295</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -2609,7 +1643,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>-24.49</v>
+        <v>-24.47</v>
       </c>
       <c r="N9" t="n">
         <v>-5</v>
@@ -2618,32 +1652,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>131.21</v>
+        <v>26.55</v>
       </c>
       <c r="D10" t="n">
-        <v>124.6495</v>
+        <v>27.8775</v>
       </c>
       <c r="E10" t="n">
-        <v>144.331</v>
+        <v>23.895</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Closed (Stop-Loss)</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2652,561 +1686,21 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46266</v>
+        <v>46288</v>
       </c>
       <c r="K10" t="n">
-        <v>124.6495</v>
+        <v>23.895</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Stop-Loss</t>
+          <t>Take-Profit</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-19.68</v>
+        <v>47.79</v>
       </c>
       <c r="N10" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GFI</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>48.21</v>
-      </c>
-      <c r="D11" t="n">
-        <v>45.4554</v>
-      </c>
-      <c r="E11" t="n">
-        <v>53.7192</v>
-      </c>
-      <c r="F11" t="n">
         <v>10</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="K11" t="n">
-        <v>45.4554</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>-27.55</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-5.71</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>IAG</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>20.97</v>
-      </c>
-      <c r="D12" t="n">
-        <v>19.9215</v>
-      </c>
-      <c r="E12" t="n">
-        <v>23.067</v>
-      </c>
-      <c r="F12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="K12" t="n">
-        <v>19.9215</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>-24.12</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AEM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>216.93</v>
-      </c>
-      <c r="D13" t="n">
-        <v>206.0835</v>
-      </c>
-      <c r="E13" t="n">
-        <v>238.623</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="K13" t="n">
-        <v>206.0835</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>-21.69</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>HLN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="D14" t="n">
-        <v>9.670999999999999</v>
-      </c>
-      <c r="E14" t="n">
-        <v>11.198</v>
-      </c>
-      <c r="F14" t="n">
-        <v>49</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="K14" t="n">
-        <v>9.670999999999999</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>-24.94</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NVO</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="D15" t="n">
-        <v>45.3245</v>
-      </c>
-      <c r="E15" t="n">
-        <v>52.481</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="K15" t="n">
-        <v>45.3245</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>-23.86</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PBR</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>17.93</v>
-      </c>
-      <c r="D16" t="n">
-        <v>18.8265</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.137</v>
-      </c>
-      <c r="F16" t="n">
-        <v>27</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="K16" t="n">
-        <v>18.8265</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>-24.21</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>79.78</v>
-      </c>
-      <c r="D17" t="n">
-        <v>75.791</v>
-      </c>
-      <c r="E17" t="n">
-        <v>87.758</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="K17" t="n">
-        <v>75.791</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>-23.93</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>LYFT</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="D18" t="n">
-        <v>16.9575</v>
-      </c>
-      <c r="E18" t="n">
-        <v>19.635</v>
-      </c>
-      <c r="F18" t="n">
-        <v>28</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="K18" t="n">
-        <v>16.9575</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>-24.99</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PLAB</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>30.91</v>
-      </c>
-      <c r="D19" t="n">
-        <v>29.3208</v>
-      </c>
-      <c r="E19" t="n">
-        <v>34.0884</v>
-      </c>
-      <c r="F19" t="n">
-        <v>16</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="K19" t="n">
-        <v>29.3208</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>-25.43</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-5.14</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ZM</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>94.76000000000001</v>
-      </c>
-      <c r="D20" t="n">
-        <v>100.5498</v>
-      </c>
-      <c r="E20" t="n">
-        <v>83.1803</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="K20" t="n">
-        <v>100.5498</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>-28.95</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-6.11</v>
       </c>
     </row>
   </sheetData>
@@ -7307,7 +5801,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7315,11 +5809,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="J76" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="K76" t="n">
+        <v>73.682</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>-23.27</v>
+      </c>
+      <c r="N76" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7703,7 +6209,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7711,11 +6217,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="J84" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="K84" t="n">
+        <v>65.2175</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>-24.03</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7949,7 +6467,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7957,11 +6475,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="J89" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="K89" t="n">
+        <v>11.1815</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>-24.72</v>
+      </c>
+      <c r="N89" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7991,7 +6521,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7999,11 +6529,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="J90" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="K90" t="n">
+        <v>33.212</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>-24.47</v>
+      </c>
+      <c r="N90" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8033,7 +6575,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8041,11 +6583,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="J91" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K91" t="n">
+        <v>69.89449999999999</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="N91" t="n">
+        <v>11.2</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8213,7 +6767,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8221,11 +6775,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="J95" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="K95" t="n">
+        <v>42.0885</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>-32.69</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-6.59</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8255,7 +6821,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8263,11 +6829,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+      <c r="J96" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K96" t="n">
+        <v>18.4794</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>-38.89</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-8.06</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8297,7 +6875,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8305,11 +6883,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="J97" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="K97" t="n">
+        <v>27.1256</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>-40.71</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-8.58</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8447,7 +7037,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8455,11 +7045,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+      <c r="J100" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="K100" t="n">
+        <v>18.0975</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>-24.77</v>
+      </c>
+      <c r="N100" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8531,7 +7133,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -8539,11 +7141,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+      <c r="J102" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K102" t="n">
+        <v>35.937</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="N102" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8681,7 +7295,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -8689,11 +7303,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+      <c r="J105" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="K105" t="n">
+        <v>22.6575</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>-23.85</v>
+      </c>
+      <c r="N105" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8723,7 +7349,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -8731,11 +7357,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
+      <c r="J106" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="K106" t="n">
+        <v>58.6055</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>-24.68</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8873,7 +7511,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8881,11 +7519,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+      <c r="J109" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="K109" t="n">
+        <v>128.06</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>-20.22</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8969,7 +7619,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8977,11 +7627,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="J111" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="K111" t="n">
+        <v>35.302</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>-24.15</v>
+      </c>
+      <c r="N111" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9065,7 +7727,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -9073,11 +7735,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+      <c r="J113" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="K113" t="n">
+        <v>13.889</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>-24.85</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9311,7 +7985,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -9319,11 +7993,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="J118" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="K118" t="n">
+        <v>77.197</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>-24.38</v>
+      </c>
+      <c r="N118" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9569,7 +8255,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9577,11 +8263,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+      <c r="J123" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K123" t="n">
+        <v>65.1605</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
+        <v>-24.01</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9665,7 +8363,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9673,11 +8371,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+      <c r="J125" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="K125" t="n">
+        <v>177.308</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M125" t="n">
+        <v>-18.66</v>
+      </c>
+      <c r="N125" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9707,7 +8417,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9715,11 +8425,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+      <c r="J126" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="K126" t="n">
+        <v>104.7755</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M126" t="n">
+        <v>-22.06</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9899,7 +8621,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9907,11 +8629,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="J130" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="K130" t="n">
+        <v>30.2295</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M130" t="n">
+        <v>-24.47</v>
+      </c>
+      <c r="N130" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9983,7 +8717,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9991,11 +8725,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="J132" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="K132" t="n">
+        <v>23.895</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M132" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="N132" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10079,7 +8825,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -10087,11 +8833,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+      <c r="J134" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="K134" t="n">
+        <v>55.407</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M134" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="N134" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10121,7 +8879,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -10129,11 +8887,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+      <c r="J135" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K135" t="n">
+        <v>39.465</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M135" t="n">
+        <v>48.23</v>
+      </c>
+      <c r="N135" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">

--- a/data/weekly_report.xlsx
+++ b/data/weekly_report.xlsx
@@ -500,44 +500,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100000</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>11.11</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>-168.15</v>
+        <v>48.96</v>
       </c>
       <c r="I2" t="n">
-        <v>85.84</v>
+        <v>-25.81</v>
       </c>
       <c r="J2" t="n">
-        <v>100389.56</v>
+        <v>100267.87</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>VICI $47.79</t>
+          <t>PFE $48.96</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>KGC $-40.71</t>
+          <t>PFE $48.96</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -714,7 +714,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200.37</v>
+        <v>235.46</v>
       </c>
       <c r="D4" t="n">
-        <v>190.3515</v>
+        <v>223.687</v>
       </c>
       <c r="E4" t="n">
-        <v>220.407</v>
+        <v>259.006</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -765,19 +765,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27.2</v>
+        <v>140.45</v>
       </c>
       <c r="D5" t="n">
-        <v>25.84</v>
+        <v>108.9013</v>
       </c>
       <c r="E5" t="n">
-        <v>29.92</v>
+        <v>161.5075</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -794,342 +794,6 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>269.77</v>
-      </c>
-      <c r="D6" t="n">
-        <v>256.2815</v>
-      </c>
-      <c r="E6" t="n">
-        <v>296.747</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CDE</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>20.33</v>
-      </c>
-      <c r="D7" t="n">
-        <v>18.5138</v>
-      </c>
-      <c r="E7" t="n">
-        <v>23.3695</v>
-      </c>
-      <c r="F7" t="n">
-        <v>24</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>46253</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FSM</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4502</v>
-      </c>
-      <c r="E8" t="n">
-        <v>13.2035</v>
-      </c>
-      <c r="F8" t="n">
-        <v>43</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>46253</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ROST</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>235.46</v>
-      </c>
-      <c r="D9" t="n">
-        <v>223.687</v>
-      </c>
-      <c r="E9" t="n">
-        <v>259.006</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>29.07</v>
-      </c>
-      <c r="D10" t="n">
-        <v>30.5235</v>
-      </c>
-      <c r="E10" t="n">
-        <v>26.163</v>
-      </c>
-      <c r="F10" t="n">
-        <v>17</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>145.21</v>
-      </c>
-      <c r="D11" t="n">
-        <v>152.4705</v>
-      </c>
-      <c r="E11" t="n">
-        <v>130.689</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ANF</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>140.45</v>
-      </c>
-      <c r="D12" t="n">
-        <v>108.9013</v>
-      </c>
-      <c r="E12" t="n">
-        <v>161.5075</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ERIC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="D13" t="n">
-        <v>10.6785</v>
-      </c>
-      <c r="E13" t="n">
-        <v>9.153</v>
-      </c>
-      <c r="F13" t="n">
-        <v>49</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1142,7 +806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1220,7 +884,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1229,23 +893,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34.96</v>
+        <v>27.2</v>
       </c>
       <c r="D2" t="n">
-        <v>33.212</v>
+        <v>25.84</v>
       </c>
       <c r="E2" t="n">
-        <v>38.456</v>
+        <v>29.92</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46252</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Closed (Stop-Loss)</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1254,452 +918,20 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46287</v>
+        <v>46315</v>
       </c>
       <c r="K2" t="n">
-        <v>33.212</v>
+        <v>29.92</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Stop-Loss</t>
+          <t>Take-Profit</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-24.47</v>
+        <v>48.96</v>
       </c>
       <c r="N2" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>45.06</v>
-      </c>
-      <c r="D3" t="n">
-        <v>42.0885</v>
-      </c>
-      <c r="E3" t="n">
-        <v>51.0029</v>
-      </c>
-      <c r="F3" t="n">
-        <v>11</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>46253</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>46289</v>
-      </c>
-      <c r="K3" t="n">
-        <v>42.0885</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>-32.69</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-6.59</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>KGC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>29.67</v>
-      </c>
-      <c r="D4" t="n">
-        <v>27.1256</v>
-      </c>
-      <c r="E4" t="n">
-        <v>34.1105</v>
-      </c>
-      <c r="F4" t="n">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>46253</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>46289</v>
-      </c>
-      <c r="K4" t="n">
-        <v>27.1256</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>-40.71</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-8.58</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22.6575</v>
-      </c>
-      <c r="E5" t="n">
-        <v>26.235</v>
-      </c>
-      <c r="F5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="K5" t="n">
-        <v>22.6575</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>-23.85</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>OXY</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>61.69</v>
-      </c>
-      <c r="D6" t="n">
-        <v>58.6055</v>
-      </c>
-      <c r="E6" t="n">
-        <v>67.85899999999999</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="K6" t="n">
-        <v>58.6055</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>-24.68</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>134.8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>128.06</v>
-      </c>
-      <c r="E7" t="n">
-        <v>148.28</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>46287</v>
-      </c>
-      <c r="K7" t="n">
-        <v>128.06</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>-20.22</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>VALE</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="D8" t="n">
-        <v>13.889</v>
-      </c>
-      <c r="E8" t="n">
-        <v>16.082</v>
-      </c>
-      <c r="F8" t="n">
-        <v>34</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>46288</v>
-      </c>
-      <c r="K8" t="n">
-        <v>13.889</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>-24.85</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ONON</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>28.79</v>
-      </c>
-      <c r="D9" t="n">
-        <v>30.2295</v>
-      </c>
-      <c r="E9" t="n">
-        <v>25.911</v>
-      </c>
-      <c r="F9" t="n">
-        <v>17</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Closed (Stop-Loss)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>46290</v>
-      </c>
-      <c r="K9" t="n">
-        <v>30.2295</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Stop-Loss</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>-24.47</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>VICI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Sell</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>26.55</v>
-      </c>
-      <c r="D10" t="n">
-        <v>27.8775</v>
-      </c>
-      <c r="E10" t="n">
-        <v>23.895</v>
-      </c>
-      <c r="F10" t="n">
-        <v>18</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Closed (Take-Profit)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>46288</v>
-      </c>
-      <c r="K10" t="n">
-        <v>23.895</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Take-Profit</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>47.79</v>
-      </c>
-      <c r="N10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6113,7 +5345,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6121,11 +5353,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="J82" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="K82" t="n">
+        <v>220.407</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>40.07</v>
+      </c>
+      <c r="N82" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6317,7 +5561,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6325,11 +5569,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="J86" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="K86" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="N86" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6629,7 +5885,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6637,11 +5893,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+      <c r="J92" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="K92" t="n">
+        <v>256.2815</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>-13.49</v>
+      </c>
+      <c r="N92" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6725,7 +5993,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6733,11 +6001,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="J94" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="K94" t="n">
+        <v>18.5138</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>-43.59</v>
+      </c>
+      <c r="N94" t="n">
+        <v>-8.93</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7091,7 +6371,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7099,11 +6379,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="J101" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="K101" t="n">
+        <v>10.4502</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>-44.71</v>
+      </c>
+      <c r="N101" t="n">
+        <v>-9.050000000000001</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8471,7 +7763,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Take-Profit)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8479,11 +7771,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+      <c r="J127" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="K127" t="n">
+        <v>26.163</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Take-Profit</t>
+        </is>
+      </c>
+      <c r="M127" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="N127" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8675,7 +7979,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8683,11 +7987,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="J131" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="K131" t="n">
+        <v>152.4705</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M131" t="n">
+        <v>-21.78</v>
+      </c>
+      <c r="N131" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9137,7 +8453,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed (Stop-Loss)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9145,11 +8461,23 @@
           <t>SEPA</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="J140" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K140" t="n">
+        <v>10.6785</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Stop-Loss</t>
+        </is>
+      </c>
+      <c r="M140" t="n">
+        <v>-24.92</v>
+      </c>
+      <c r="N140" t="n">
+        <v>-5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
